--- a/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_PYRAD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.75 ± 0.08</t>
+          <t>0.73 ± 0.08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.62 ± 0.10</t>
+          <t>0.56 ± 0.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73 ± 0.16</t>
+          <t>0.70 ± 0.20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.23</t>
+          <t>0.51 ± 0.20</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.61 ± 0.22</t>
+          <t>0.49 ± 0.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.59 ± 0.21</t>
+          <t>0.62 ± 0.22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="F4" t="n">
